--- a/salon_forms/018_patch_test_consent_form--salon_forms.xlsx
+++ b/salon_forms/018_patch_test_consent_form--salon_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>consent_date</t>
+          <t>consent_date_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Consent Date 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>test_result</t>
+          <t>test_result_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Test Result</t>
+          <t>Test Result 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Treatment Date</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Treatment Time</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>patch_test_consent</t>
+          <t>patch_test_consent_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Patch Test Date</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
   <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1421,7 +1421,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>test_result_choices</t>
+          <t>test_result_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1438,7 +1438,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>test_result_choices</t>
+          <t>test_result_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1506,7 +1506,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>patch_test_consent_choices</t>
+          <t>patch_test_consent_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>patch_test_consent_choices</t>
+          <t>patch_test_consent_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
